--- a/templates/ACE_Import_Template.xlsx
+++ b/templates/ACE_Import_Template.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AG1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="23.83203125" customWidth="1"/>
@@ -419,16 +419,21 @@
     <col min="16" max="16" width="15.83203125" customWidth="1"/>
     <col min="17" max="17" width="13.83203125" customWidth="1"/>
     <col min="18" max="18" width="12.83203125" customWidth="1"/>
-    <col min="19" max="19" width="14.83203125" customWidth="1"/>
-    <col min="20" max="20" width="14.83203125" customWidth="1"/>
-    <col min="21" max="21" width="16.83203125" customWidth="1"/>
-    <col min="22" max="22" width="12.83203125" customWidth="1"/>
-    <col min="23" max="23" width="12.83203125" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
-    <col min="25" max="25" width="15.83203125" customWidth="1"/>
-    <col min="26" max="26" width="17.83203125" customWidth="1"/>
+    <col min="19" max="19" width="16.83203125" customWidth="1"/>
+    <col min="20" max="20" width="12.83203125" customWidth="1"/>
+    <col min="21" max="21" width="13.83203125" customWidth="1"/>
+    <col min="22" max="22" width="18.83203125" customWidth="1"/>
+    <col min="23" max="23" width="15.83203125" customWidth="1"/>
+    <col min="24" max="24" width="14.83203125" customWidth="1"/>
+    <col min="25" max="25" width="14.83203125" customWidth="1"/>
+    <col min="26" max="26" width="16.83203125" customWidth="1"/>
     <col min="27" max="27" width="12.83203125" customWidth="1"/>
-    <col min="28" max="28" width="13.83203125" customWidth="1"/>
+    <col min="28" max="28" width="12.83203125" customWidth="1"/>
+    <col min="29" max="29" width="12.83203125" customWidth="1"/>
+    <col min="30" max="30" width="15.83203125" customWidth="1"/>
+    <col min="31" max="31" width="17.83203125" customWidth="1"/>
+    <col min="32" max="32" width="12.83203125" customWidth="1"/>
+    <col min="33" max="33" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,46 +492,61 @@
         <v>BillTo</v>
       </c>
       <c r="S1" t="str">
+        <v>BillToAddress2</v>
+      </c>
+      <c r="T1" t="str">
+        <v>BillToCity</v>
+      </c>
+      <c r="U1" t="str">
+        <v>BillToState</v>
+      </c>
+      <c r="V1" t="str">
+        <v>BillToPostalCode</v>
+      </c>
+      <c r="W1" t="str">
+        <v>BillToCountry</v>
+      </c>
+      <c r="X1" t="str">
         <v>FreightTerms</v>
       </c>
-      <c r="T1" t="str">
+      <c r="Y1" t="str">
         <v>PaymentTerms</v>
       </c>
-      <c r="U1" t="str">
+      <c r="Z1" t="str">
         <v>PaymentDueDate</v>
       </c>
-      <c r="V1" t="str">
+      <c r="AA1" t="str">
         <v>PONumber</v>
       </c>
-      <c r="W1" t="str">
+      <c r="AB1" t="str">
         <v>Carrier</v>
       </c>
-      <c r="X1" t="str">
+      <c r="AC1" t="str">
         <v>Vessel</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AD1" t="str">
         <v>BookingNumber</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AE1" t="str">
         <v>ContainerNumber</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AF1" t="str">
         <v>SealNumber</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AG1" t="str">
         <v>Destination</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AB1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AG1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AG3"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="23.83203125" customWidth="1"/>
@@ -545,17 +565,22 @@
     <col min="15" max="15" width="25.83203125" customWidth="1"/>
     <col min="16" max="16" width="15.83203125" customWidth="1"/>
     <col min="17" max="17" width="13.83203125" customWidth="1"/>
-    <col min="18" max="18" width="32.83203125" customWidth="1"/>
-    <col min="19" max="19" width="14.83203125" customWidth="1"/>
-    <col min="20" max="20" width="14.83203125" customWidth="1"/>
-    <col min="21" max="21" width="16.83203125" customWidth="1"/>
-    <col min="22" max="22" width="10.83203125" customWidth="1"/>
-    <col min="23" max="23" width="25.83203125" customWidth="1"/>
+    <col min="18" max="18" width="17.83203125" customWidth="1"/>
+    <col min="19" max="19" width="22.83203125" customWidth="1"/>
+    <col min="20" max="20" width="12.83203125" customWidth="1"/>
+    <col min="21" max="21" width="13.83203125" customWidth="1"/>
+    <col min="22" max="22" width="18.83203125" customWidth="1"/>
+    <col min="23" max="23" width="15.83203125" customWidth="1"/>
     <col min="24" max="24" width="14.83203125" customWidth="1"/>
-    <col min="25" max="25" width="15.83203125" customWidth="1"/>
-    <col min="26" max="26" width="17.83203125" customWidth="1"/>
-    <col min="27" max="27" width="12.83203125" customWidth="1"/>
-    <col min="28" max="28" width="13.83203125" customWidth="1"/>
+    <col min="25" max="25" width="14.83203125" customWidth="1"/>
+    <col min="26" max="26" width="16.83203125" customWidth="1"/>
+    <col min="27" max="27" width="10.83203125" customWidth="1"/>
+    <col min="28" max="28" width="25.83203125" customWidth="1"/>
+    <col min="29" max="29" width="14.83203125" customWidth="1"/>
+    <col min="30" max="30" width="15.83203125" customWidth="1"/>
+    <col min="31" max="31" width="17.83203125" customWidth="1"/>
+    <col min="32" max="32" width="12.83203125" customWidth="1"/>
+    <col min="33" max="33" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -614,33 +639,48 @@
         <v>BillTo</v>
       </c>
       <c r="S1" t="str">
+        <v>BillToAddress2</v>
+      </c>
+      <c r="T1" t="str">
+        <v>BillToCity</v>
+      </c>
+      <c r="U1" t="str">
+        <v>BillToState</v>
+      </c>
+      <c r="V1" t="str">
+        <v>BillToPostalCode</v>
+      </c>
+      <c r="W1" t="str">
+        <v>BillToCountry</v>
+      </c>
+      <c r="X1" t="str">
         <v>FreightTerms</v>
       </c>
-      <c r="T1" t="str">
+      <c r="Y1" t="str">
         <v>PaymentTerms</v>
       </c>
-      <c r="U1" t="str">
+      <c r="Z1" t="str">
         <v>PaymentDueDate</v>
       </c>
-      <c r="V1" t="str">
+      <c r="AA1" t="str">
         <v>PONumber</v>
       </c>
-      <c r="W1" t="str">
+      <c r="AB1" t="str">
         <v>Carrier</v>
       </c>
-      <c r="X1" t="str">
+      <c r="AC1" t="str">
         <v>Vessel</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AD1" t="str">
         <v>BookingNumber</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AE1" t="str">
         <v>ContainerNumber</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AF1" t="str">
         <v>SealNumber</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AG1" t="str">
         <v>Destination</v>
       </c>
     </row>
@@ -697,36 +737,51 @@
         <v>2026-03-12</v>
       </c>
       <c r="R2" t="str">
-        <v>14 HARBOUR ROAD, HAIFA, ISRAEL</v>
+        <v>14 HARBOUR ROAD</v>
       </c>
       <c r="S2" t="str">
+        <v>PORT INDUSTRIAL ZONE</v>
+      </c>
+      <c r="T2" t="str">
+        <v>HAIFA</v>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v>3303201</v>
+      </c>
+      <c r="W2" t="str">
+        <v>IL</v>
+      </c>
+      <c r="X2" t="str">
         <v>CIF</v>
       </c>
-      <c r="T2" t="str">
+      <c r="Y2" t="str">
         <v>NET 30</v>
       </c>
-      <c r="U2" t="str">
+      <c r="Z2" t="str">
         <v>2026-04-11</v>
       </c>
-      <c r="V2" t="str">
+      <c r="AA2" t="str">
         <v>PO-88213</v>
       </c>
-      <c r="W2" t="str">
+      <c r="AB2" t="str">
         <v>ZIM INTEGRATED SHIPPING</v>
       </c>
-      <c r="X2" t="str">
+      <c r="AC2" t="str">
         <v>ZIM SHANGHAI</v>
       </c>
-      <c r="Y2" t="str">
+      <c r="AD2" t="str">
         <v>BKG-5541220</v>
       </c>
-      <c r="Z2" t="str">
+      <c r="AE2" t="str">
         <v>ZIMU1234567</v>
       </c>
-      <c r="AA2" t="str">
+      <c r="AF2" t="str">
         <v>SL-99401</v>
       </c>
-      <c r="AB2" t="str">
+      <c r="AG2" t="str">
         <v>IL</v>
       </c>
     </row>
@@ -815,17 +870,32 @@
       <c r="AB3" t="str">
         <v/>
       </c>
+      <c r="AC3" t="str">
+        <v/>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AB3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AG3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B38"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="110.83203125" customWidth="1"/>
@@ -1004,7 +1074,7 @@
         <v>CustomerName</v>
       </c>
       <c r="B22" t="str">
-        <v>Ultimate consignee name.</v>
+        <v>Ultimate consignee company name (ACE Parties step, Ultimate Consignee panel).</v>
       </c>
     </row>
     <row r="23">
@@ -1012,7 +1082,7 @@
         <v>InvoiceNumber</v>
       </c>
       <c r="B23" t="str">
-        <v>Becomes the ACE shipment reference (17 characters maximum).</v>
+        <v>Becomes the ACE Shipment Reference Number (17 characters maximum).</v>
       </c>
     </row>
     <row r="24">
@@ -1020,7 +1090,7 @@
         <v>InvoiceDate</v>
       </c>
       <c r="B24" t="str">
-        <v>YYYY-MM-DD, MM/DD/YYYY, or a real Excel date. Filed as MM/DD/YYYY.</v>
+        <v>YYYY-MM-DD, MM/DD/YYYY, or a real Excel date. Filed as the ACE Departure Date, MM/DD/YYYY.</v>
       </c>
     </row>
     <row r="25">
@@ -1028,76 +1098,116 @@
         <v>BillTo</v>
       </c>
       <c r="B25" t="str">
-        <v>Consignee address.</v>
+        <v>Consignee street address, line 1 (ACE "Address Line 1").</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>FreightTerms</v>
+        <v>BillToAddress2</v>
       </c>
       <c r="B26" t="str">
-        <v>INCO terms / terms of sale, e.g. CIF, FOB.</v>
+        <v>Consignee address, line 2. Optional.</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>PaymentTerms / PaymentDueDate</v>
+        <v>BillToCity</v>
       </c>
       <c r="B27" t="str">
-        <v>Carried for reference and for the future QuickBooks phase; not filed in AES.</v>
+        <v>Consignee city.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>PONumber</v>
+        <v>BillToState</v>
       </c>
       <c r="B28" t="str">
-        <v>Customer purchase order.</v>
+        <v>Consignee state or province code. Only needed for countries that have them (US, CA, MX).</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Carrier / Vessel / BookingNumber</v>
+        <v>BillToPostalCode</v>
       </c>
       <c r="B29" t="str">
-        <v>Transportation step values.</v>
+        <v>Consignee postal code. Only needed for countries that require one.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ContainerNumber / SealNumber</v>
+        <v>BillToCountry</v>
       </c>
       <c r="B30" t="str">
-        <v>Container and seal, ISO 6346 format for the container (4 letters + 7 digits).</v>
+        <v>Consignee country, ISO 3166-1 alpha-2 (TR, IL, DE). Common country names are converted.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Destination</v>
+        <v>FreightTerms</v>
       </c>
       <c r="B31" t="str">
-        <v>Country of ultimate destination, ISO 3166-1 alpha-2 (IL, CA, DE). Common country names are converted.</v>
+        <v>INCO terms / terms of sale, e.g. CIF, FOB. Carried for reference; the ACE Shipment step has no such field.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v/>
+        <v>PaymentTerms / PaymentDueDate</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>Carried for reference and for the QuickBooks phase; not filed in AES.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
+        <v>PONumber</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Customer purchase order. Carried for reference; the ACE Shipment step has no such field.</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Carrier / Vessel / BookingNumber</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Transportation step values.</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>ContainerNumber / SealNumber</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Container and seal, ISO 6346 format for the container (4 letters + 7 digits).</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Destination</v>
+      </c>
+      <c r="B36" t="str">
+        <v>ACE Country of Destination, ISO 3166-1 alpha-2 (IL, CA, DE). Common country names are converted.</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v/>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
         <v>Reminder</v>
       </c>
-      <c r="B33" t="str">
+      <c r="B38" t="str">
         <v>ACE Helper never saves a line, submits, or certifies a filing. Review every populated field in ACE and submit it yourself.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B38"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/templates/ACE_Import_Template.xlsx
+++ b/templates/ACE_Import_Template.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="23.83203125" customWidth="1"/>
@@ -424,16 +424,17 @@
     <col min="21" max="21" width="13.83203125" customWidth="1"/>
     <col min="22" max="22" width="18.83203125" customWidth="1"/>
     <col min="23" max="23" width="15.83203125" customWidth="1"/>
-    <col min="24" max="24" width="14.83203125" customWidth="1"/>
+    <col min="24" max="24" width="13.83203125" customWidth="1"/>
     <col min="25" max="25" width="14.83203125" customWidth="1"/>
-    <col min="26" max="26" width="16.83203125" customWidth="1"/>
-    <col min="27" max="27" width="12.83203125" customWidth="1"/>
+    <col min="26" max="26" width="14.83203125" customWidth="1"/>
+    <col min="27" max="27" width="16.83203125" customWidth="1"/>
     <col min="28" max="28" width="12.83203125" customWidth="1"/>
     <col min="29" max="29" width="12.83203125" customWidth="1"/>
-    <col min="30" max="30" width="15.83203125" customWidth="1"/>
-    <col min="31" max="31" width="17.83203125" customWidth="1"/>
-    <col min="32" max="32" width="12.83203125" customWidth="1"/>
-    <col min="33" max="33" width="13.83203125" customWidth="1"/>
+    <col min="30" max="30" width="12.83203125" customWidth="1"/>
+    <col min="31" max="31" width="15.83203125" customWidth="1"/>
+    <col min="32" max="32" width="17.83203125" customWidth="1"/>
+    <col min="33" max="33" width="12.83203125" customWidth="1"/>
+    <col min="34" max="34" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,46 +508,49 @@
         <v>BillToCountry</v>
       </c>
       <c r="X1" t="str">
+        <v>OriginState</v>
+      </c>
+      <c r="Y1" t="str">
         <v>FreightTerms</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="Z1" t="str">
         <v>PaymentTerms</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AA1" t="str">
         <v>PaymentDueDate</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AB1" t="str">
         <v>PONumber</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AC1" t="str">
         <v>Carrier</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AD1" t="str">
         <v>Vessel</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AE1" t="str">
         <v>BookingNumber</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AF1" t="str">
         <v>ContainerNumber</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AG1" t="str">
         <v>SealNumber</v>
       </c>
-      <c r="AG1" t="str">
+      <c r="AH1" t="str">
         <v>Destination</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AG1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AH1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG3"/>
+  <dimension ref="A1:AH3"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="23.83203125" customWidth="1"/>
@@ -571,16 +575,17 @@
     <col min="21" max="21" width="13.83203125" customWidth="1"/>
     <col min="22" max="22" width="18.83203125" customWidth="1"/>
     <col min="23" max="23" width="15.83203125" customWidth="1"/>
-    <col min="24" max="24" width="14.83203125" customWidth="1"/>
+    <col min="24" max="24" width="13.83203125" customWidth="1"/>
     <col min="25" max="25" width="14.83203125" customWidth="1"/>
-    <col min="26" max="26" width="16.83203125" customWidth="1"/>
-    <col min="27" max="27" width="10.83203125" customWidth="1"/>
-    <col min="28" max="28" width="25.83203125" customWidth="1"/>
-    <col min="29" max="29" width="14.83203125" customWidth="1"/>
-    <col min="30" max="30" width="15.83203125" customWidth="1"/>
-    <col min="31" max="31" width="17.83203125" customWidth="1"/>
-    <col min="32" max="32" width="12.83203125" customWidth="1"/>
-    <col min="33" max="33" width="13.83203125" customWidth="1"/>
+    <col min="26" max="26" width="14.83203125" customWidth="1"/>
+    <col min="27" max="27" width="16.83203125" customWidth="1"/>
+    <col min="28" max="28" width="10.83203125" customWidth="1"/>
+    <col min="29" max="29" width="25.83203125" customWidth="1"/>
+    <col min="30" max="30" width="14.83203125" customWidth="1"/>
+    <col min="31" max="31" width="15.83203125" customWidth="1"/>
+    <col min="32" max="32" width="17.83203125" customWidth="1"/>
+    <col min="33" max="33" width="12.83203125" customWidth="1"/>
+    <col min="34" max="34" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -654,33 +659,36 @@
         <v>BillToCountry</v>
       </c>
       <c r="X1" t="str">
+        <v>OriginState</v>
+      </c>
+      <c r="Y1" t="str">
         <v>FreightTerms</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="Z1" t="str">
         <v>PaymentTerms</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AA1" t="str">
         <v>PaymentDueDate</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AB1" t="str">
         <v>PONumber</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AC1" t="str">
         <v>Carrier</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AD1" t="str">
         <v>Vessel</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AE1" t="str">
         <v>BookingNumber</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AF1" t="str">
         <v>ContainerNumber</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AG1" t="str">
         <v>SealNumber</v>
       </c>
-      <c r="AG1" t="str">
+      <c r="AH1" t="str">
         <v>Destination</v>
       </c>
     </row>
@@ -755,33 +763,36 @@
         <v>IL</v>
       </c>
       <c r="X2" t="str">
+        <v>CA</v>
+      </c>
+      <c r="Y2" t="str">
         <v>CIF</v>
       </c>
-      <c r="Y2" t="str">
+      <c r="Z2" t="str">
         <v>NET 30</v>
       </c>
-      <c r="Z2" t="str">
+      <c r="AA2" t="str">
         <v>2026-04-11</v>
       </c>
-      <c r="AA2" t="str">
+      <c r="AB2" t="str">
         <v>PO-88213</v>
       </c>
-      <c r="AB2" t="str">
+      <c r="AC2" t="str">
         <v>ZIM INTEGRATED SHIPPING</v>
       </c>
-      <c r="AC2" t="str">
+      <c r="AD2" t="str">
         <v>ZIM SHANGHAI</v>
       </c>
-      <c r="AD2" t="str">
+      <c r="AE2" t="str">
         <v>BKG-5541220</v>
       </c>
-      <c r="AE2" t="str">
+      <c r="AF2" t="str">
         <v>ZIMU1234567</v>
       </c>
-      <c r="AF2" t="str">
+      <c r="AG2" t="str">
         <v>SL-99401</v>
       </c>
-      <c r="AG2" t="str">
+      <c r="AH2" t="str">
         <v>IL</v>
       </c>
     </row>
@@ -885,17 +896,20 @@
       <c r="AG3" t="str">
         <v/>
       </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AG3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AH3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B39"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="110.83203125" customWidth="1"/>
@@ -1143,71 +1157,79 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>FreightTerms</v>
+        <v>OriginState</v>
       </c>
       <c r="B31" t="str">
-        <v>INCO terms / terms of sale, e.g. CIF, FOB. Carried for reference; the ACE Shipment step has no such field.</v>
+        <v>ACE Step 1 Origin State: the US state the goods COME FROM, not the state of the export port. Almonds railed from northern California to Norfolk are CA, not VA. Two-letter code; state names are converted.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>PaymentTerms / PaymentDueDate</v>
+        <v>FreightTerms</v>
       </c>
       <c r="B32" t="str">
-        <v>Carried for reference and for the QuickBooks phase; not filed in AES.</v>
+        <v>INCO terms / terms of sale, e.g. CIF, FOB. Carried for reference; the ACE Shipment step has no such field.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>PONumber</v>
+        <v>PaymentTerms / PaymentDueDate</v>
       </c>
       <c r="B33" t="str">
-        <v>Customer purchase order. Carried for reference; the ACE Shipment step has no such field.</v>
+        <v>Carried for reference and for the QuickBooks phase; not filed in AES.</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Carrier / Vessel / BookingNumber</v>
+        <v>PONumber</v>
       </c>
       <c r="B34" t="str">
-        <v>Transportation step values.</v>
+        <v>Customer purchase order. Carried for reference; the ACE Shipment step has no such field.</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ContainerNumber / SealNumber</v>
+        <v>Carrier / Vessel / BookingNumber</v>
       </c>
       <c r="B35" t="str">
-        <v>Container and seal, ISO 6346 format for the container (4 letters + 7 digits).</v>
+        <v>Transportation step values.</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Destination</v>
+        <v>ContainerNumber / SealNumber</v>
       </c>
       <c r="B36" t="str">
-        <v>ACE Country of Destination, ISO 3166-1 alpha-2 (IL, CA, DE). Common country names are converted.</v>
+        <v>Container and seal, ISO 6346 format for the container (4 letters + 7 digits).</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v/>
+        <v>Destination</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>ACE Country of Destination, ISO 3166-1 alpha-2 (IL, CA, DE). Common country names are converted.</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
+        <v/>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
         <v>Reminder</v>
       </c>
-      <c r="B38" t="str">
+      <c r="B39" t="str">
         <v>ACE Helper never saves a line, submits, or certifies a filing. Review every populated field in ACE and submit it yourself.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B39"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/templates/ACE_Import_Template.xlsx
+++ b/templates/ACE_Import_Template.xlsx
@@ -580,7 +580,7 @@
     <col min="26" max="26" width="14.83203125" customWidth="1"/>
     <col min="27" max="27" width="16.83203125" customWidth="1"/>
     <col min="28" max="28" width="10.83203125" customWidth="1"/>
-    <col min="29" max="29" width="25.83203125" customWidth="1"/>
+    <col min="29" max="29" width="10.83203125" customWidth="1"/>
     <col min="30" max="30" width="14.83203125" customWidth="1"/>
     <col min="31" max="31" width="15.83203125" customWidth="1"/>
     <col min="32" max="32" width="17.83203125" customWidth="1"/>
@@ -778,7 +778,7 @@
         <v>PO-88213</v>
       </c>
       <c r="AC2" t="str">
-        <v>ZIM INTEGRATED SHIPPING</v>
+        <v>ZIMU</v>
       </c>
       <c r="AD2" t="str">
         <v>ZIM SHANGHAI</v>
@@ -787,7 +787,7 @@
         <v>BKG-5541220</v>
       </c>
       <c r="AF2" t="str">
-        <v>ZIMU1234567</v>
+        <v>ZIMU1234569</v>
       </c>
       <c r="AG2" t="str">
         <v>SL-99401</v>
@@ -1192,7 +1192,7 @@
         <v>Carrier / Vessel / BookingNumber</v>
       </c>
       <c r="B35" t="str">
-        <v>Transportation step values.</v>
+        <v>Transportation step values. Carrier is the 4-letter SCAC (ZIMU, MSCU), which is what ACE Step 4 asks for; a carrier name draws a warning.</v>
       </c>
     </row>
     <row r="36">
